--- a/TeplosilaWeb/Content/properties/htrv3s.xlsx
+++ b/TeplosilaWeb/Content/properties/htrv3s.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user29\Documents\ТЗ программа подбора TRV, RDT\ТЗ клапаны TRV\25.05.2026 (действ)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/22451d98f477d1d3/Рабочий стол/TeploSilaWeb/TeplosilaWeb/Content/properties/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35AF5A0-26F8-4C6C-B053-DA1AFF147A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{10798E6F-A266-4E57-AFD9-CAB3572478BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,9 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -123,12 +126,6 @@
     <t>TSL-3000-60-2A-230-IP67</t>
   </si>
   <si>
-    <t>TW5000-XD220-S.14</t>
-  </si>
-  <si>
-    <t>1 (60); 2 (30)</t>
-  </si>
-  <si>
     <t>TSL-1600-25-2AR-230-IP67</t>
   </si>
   <si>
@@ -175,6 +172,12 @@
   </si>
   <si>
     <t>TSL-3000-60-2М-230-IP67</t>
+  </si>
+  <si>
+    <t>TSL-10000-60-3A-230-IP65</t>
+  </si>
+  <si>
+    <t>1,5 (40)</t>
   </si>
 </sst>
 </file>
@@ -325,7 +328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -353,6 +356,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -364,9 +376,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -667,49 +676,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="14"/>
+      <c r="A1" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+      <c r="V1" s="17"/>
+      <c r="W1" s="17"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B2" s="3">
         <v>53</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C2" s="18">
         <v>54</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3">
         <v>55</v>
@@ -740,88 +749,88 @@
       </c>
     </row>
     <row r="3" spans="1:23" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="15" t="s">
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="15" t="s">
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="R3" s="15" t="s">
+      <c r="R3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="S3" s="15" t="s">
+      <c r="S3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="T3" s="15"/>
-      <c r="U3" s="15" t="s">
+      <c r="T3" s="13"/>
+      <c r="U3" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="V3" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="W3" s="15" t="s">
+      <c r="V3" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="W3" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:23" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="11" t="s">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="15" t="s">
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="P4" s="15" t="s">
+      <c r="P4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
-      <c r="S4" s="15" t="s">
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="T4" s="15" t="s">
+      <c r="T4" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="U4" s="15"/>
-      <c r="V4" s="15"/>
-      <c r="W4" s="15"/>
+      <c r="U4" s="13"/>
+      <c r="V4" s="13"/>
+      <c r="W4" s="13"/>
     </row>
     <row r="5" spans="1:23" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
       <c r="C5" s="5">
         <v>15</v>
       </c>
@@ -858,22 +867,22 @@
       <c r="N5" s="5">
         <v>200</v>
       </c>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15"/>
-      <c r="T5" s="15"/>
-      <c r="U5" s="15"/>
-      <c r="V5" s="15"/>
-      <c r="W5" s="15"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="13"/>
+      <c r="V5" s="13"/>
+      <c r="W5" s="13"/>
     </row>
     <row r="6" spans="1:23" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>45</v>
+      <c r="B6" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="C6" s="6">
         <v>16</v>
@@ -991,7 +1000,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C8" s="6">
         <v>16</v>
@@ -1050,7 +1059,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C9" s="6">
         <v>16</v>
@@ -1227,7 +1236,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C12" s="6">
         <v>16</v>
@@ -1345,7 +1354,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C14" s="6">
         <v>16</v>
@@ -1403,8 +1412,8 @@
       <c r="A15" s="6">
         <v>10</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>46</v>
+      <c r="B15" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -1510,7 +1519,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -1563,7 +1572,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -1722,7 +1731,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
@@ -1828,7 +1837,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -1880,8 +1889,8 @@
       <c r="A24" s="6">
         <v>19</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>47</v>
+      <c r="B24" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
@@ -1932,7 +1941,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
@@ -1983,7 +1992,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
@@ -2034,7 +2043,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="10"/>
@@ -2232,59 +2241,56 @@
       </c>
     </row>
     <row r="31" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
+      <c r="A31" s="11">
         <v>26</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="6">
-        <v>1.5</v>
-      </c>
-      <c r="O31" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="P31" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q31" s="6">
-        <v>5000</v>
-      </c>
-      <c r="R31" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="S31" s="6" t="s">
+      <c r="B31" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11">
+        <v>3.3</v>
+      </c>
+      <c r="O31" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P31" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q31" s="11">
+        <v>10000</v>
+      </c>
+      <c r="R31" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="S31" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="T31" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="U31" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="V31" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="W31" s="6">
-        <v>30</v>
+      <c r="T31" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="U31" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="V31" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="W31" s="11">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:N3"/>
-    <mergeCell ref="C4:N4"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="W3:W5"/>
     <mergeCell ref="C2:M2"/>
@@ -2299,6 +2305,9 @@
     <mergeCell ref="Q3:Q5"/>
     <mergeCell ref="R3:R5"/>
     <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:N3"/>
+    <mergeCell ref="C4:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/TeplosilaWeb/Content/properties/htrv3s.xlsx
+++ b/TeplosilaWeb/Content/properties/htrv3s.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/22451d98f477d1d3/Рабочий стол/TeploSilaWeb/TeplosilaWeb/Content/properties/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{10798E6F-A266-4E57-AFD9-CAB3572478BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6C5C603-5E35-4BE2-9338-95B92052091A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="49">
   <si>
     <t>Условный диаметр DN, мм</t>
   </si>
@@ -178,6 +178,9 @@
   </si>
   <si>
     <t>1,5 (40)</t>
+  </si>
+  <si>
+    <t>TSL-5000-60-2A-230-IP67</t>
   </si>
 </sst>
 </file>
@@ -362,9 +365,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -376,6 +376,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -660,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W31"/>
+  <dimension ref="A1:W32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="4" customWidth="1"/>
@@ -676,31 +679,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B2" s="3">
@@ -749,88 +752,88 @@
       </c>
     </row>
     <row r="3" spans="1:23" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="16"/>
-      <c r="O3" s="13" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13" t="s">
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="R3" s="13" t="s">
+      <c r="R3" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="S3" s="13" t="s">
+      <c r="S3" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13" t="s">
+      <c r="T3" s="17"/>
+      <c r="U3" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="V3" s="13" t="s">
+      <c r="V3" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="W3" s="13" t="s">
+      <c r="W3" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:23" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="14" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="13" t="s">
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="P4" s="13" t="s">
+      <c r="P4" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="13" t="s">
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="T4" s="13" t="s">
+      <c r="T4" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U4" s="13"/>
-      <c r="V4" s="13"/>
-      <c r="W4" s="13"/>
+      <c r="U4" s="17"/>
+      <c r="V4" s="17"/>
+      <c r="W4" s="17"/>
     </row>
     <row r="5" spans="1:23" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
       <c r="C5" s="5">
         <v>15</v>
       </c>
@@ -867,15 +870,15 @@
       <c r="N5" s="5">
         <v>200</v>
       </c>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="13"/>
-      <c r="V5" s="13"/>
-      <c r="W5" s="13"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="17"/>
+      <c r="V5" s="17"/>
+      <c r="W5" s="17"/>
     </row>
     <row r="6" spans="1:23" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
@@ -2192,105 +2195,156 @@
       </c>
     </row>
     <row r="30" spans="1:23" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A30" s="6">
+      <c r="A30" s="11">
         <v>25</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="O30" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P30" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q30" s="11">
+        <v>5000</v>
+      </c>
+      <c r="R30" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="S30" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="T30" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="U30" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="V30" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="W30" s="11">
         <v>20</v>
       </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
-      <c r="N30" s="6">
+    </row>
+    <row r="31" spans="1:23" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A31" s="6">
+        <v>26</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6">
         <v>2</v>
       </c>
-      <c r="O30" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="P30" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q30" s="6">
+      <c r="O31" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="P31" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q31" s="6">
         <v>6000</v>
       </c>
-      <c r="R30" s="8" t="s">
+      <c r="R31" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="S30" s="6" t="s">
+      <c r="S31" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="T30" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="U30" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="V30" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="W30" s="6">
+      <c r="T31" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="U31" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="V31" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="W31" s="6">
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="11">
-        <v>26</v>
-      </c>
-      <c r="B31" s="9" t="s">
+    <row r="32" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>27</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="11">
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6">
         <v>3.3</v>
       </c>
-      <c r="O31" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="P31" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q31" s="11">
+      <c r="O32" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="P32" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q32" s="6">
         <v>10000</v>
       </c>
-      <c r="R31" s="12" t="s">
+      <c r="R32" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="S31" s="11" t="s">
+      <c r="S32" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="T31" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="U31" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="V31" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="W31" s="11">
+      <c r="T32" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="U32" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="V32" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="W32" s="6">
         <v>150</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C3:N3"/>
+    <mergeCell ref="C4:N4"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="W3:W5"/>
     <mergeCell ref="C2:M2"/>
@@ -2306,8 +2360,6 @@
     <mergeCell ref="R3:R5"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:N3"/>
-    <mergeCell ref="C4:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
